--- a/PTBR/Lang/PTBR/Dialog/Drama/fairy_nanasu.xlsx
+++ b/PTBR/Lang/PTBR/Dialog/Drama/fairy_nanasu.xlsx
@@ -405,7 +405,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:L61"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8.85" customWidth="1" style="16" min="1" max="1"/>
     <col width="19.85" customWidth="1" style="16" min="2" max="2"/>
@@ -515,9 +515,9 @@
           <t>I’m Nanasu, the eggplant fairy!</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Eu sou a Nanasu, a fada berinjela!</t>
+      <c r="L8" s="16" t="inlineStr">
+        <is>
+          <t>Sou a Nanasu, a fada da berinjela!</t>
         </is>
       </c>
     </row>
@@ -555,9 +555,9 @@
           <t>Is something troubling you?</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Algo está te incomodando?</t>
+      <c r="L9" s="16" t="inlineStr">
+        <is>
+          <t>Algo te perturba?</t>
         </is>
       </c>
     </row>
@@ -590,9 +590,9 @@
           <t>Here is your Bag of Holding.</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Aqui está sua Bolsa de Armazenamento.</t>
+      <c r="L10" s="16" t="inlineStr">
+        <is>
+          <t>Aqui está sua Bolsa Guarda-Tudo.</t>
         </is>
       </c>
     </row>
@@ -645,10 +645,10 @@
 There’s this rumor going around among the adventurers visiting Specwing. They say a certain Nefia hides a treasure beyond imagination! Supposedly, it’s a mysterious bag that makes anything you put inside feel lighter.</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Oh? Você não é um aventureiro? Heehee, que timing perfeito! Na verdade, tenho um pequeno favor para pedir... você me escuta?
-Tem um boato circulando entre os aventureiros que visitam Specwing. Dizem que certa Nefia esconde um tesouro além da imaginação! Supostamente, é uma bolsa misteriosa que faz qualquer coisa que você coloque dentro parecer mais leve.</t>
+      <c r="L19" s="16" t="inlineStr">
+        <is>
+          <t>Oh? Você não é um aventureiro? Hihi, hora perfeita! Na verdade tenho um favorzinho a pedir... você me ouve?
+Corre este rumor entre os aventureiros que visitam Specwing. Dizem que certa Nefia esconde um tesouro além da imaginação! Dizem que é uma bolsa misteriosa que faz qualquer coisa que você puser dentro ficar mais leve.</t>
         </is>
       </c>
     </row>
@@ -666,9 +666,9 @@
           <t>You know how I’m not very strong, right? My pack always ends up too heavy, and sometimes I feel like crying in the middle of a trip. But if I had that bag, I could go farther than ever before! I could meet more people, and every adventure would become even more fun.</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Você sabe que eu não sou muito forte, né? Minha mochila sempre acaba ficando pesada demais, e às vezes eu sinto vontade de chorar no meio de uma viagem. Mas se eu tivesse essa bolsa, poderia ir mais longe do que nunca! Poderia conhecer mais pessoas, e cada aventura se tornaria ainda mais divertida.</t>
+      <c r="L20" s="16" t="inlineStr">
+        <is>
+          <t>Você sabe que eu não sou muito forte, né? Minha mochila sempre acaba pesada demais, e às vezes sinto vontade de chorar no meio de uma viagem. Mas se eu tivesse aquela bolsa, poderia ir mais longe que nunca! Poderia conhecer mais gente, e cada aventura ficaria ainda mais divertida.</t>
         </is>
       </c>
     </row>
@@ -690,11 +690,11 @@
 And don’t worry, I’ll pay you back too. How about some rare tree seeds you’d never see in the human lands?</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Mas, hmm... a Floresta do Caminho Perdido é um pouco assustadora demais para eu explorar sozinha. Então, aventureiro... Você viria comigo?
-Tenho essa sensação—tipo, com você, vai ficar tudo bem. Você é forte, confiável e, acima de tudo... eu sei que uma aventura com você vai ser emocionante!
-E não se preocupe, eu vou te recompensar também. Que tal algumas sementes raras de árvores que você nunca veria nas terras humanas?</t>
+      <c r="L21" s="16" t="inlineStr">
+        <is>
+          <t>Mas, hum... a Floresta do Caminho Perdido é um pouco assustadora demais para eu explorar sozinha. Então, aventureiro... Você viria comigo?
+Tenho um pressentimento: tipo, com você, vai dar tudo certo. Você é forte, confiável e, acima de tudo... sei que uma aventura com você vai ser emocionante!
+E não se preocupe, vou recompensar você também. Que tal umas sementes de árvores raras que você nunca veria nas terras humanas?</t>
         </is>
       </c>
     </row>
@@ -722,9 +722,9 @@
           <t>I accept. (Danger Level: 20)</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Eu aceito. (Nível de Perigo: 20)</t>
+      <c r="L23" s="16" t="inlineStr">
+        <is>
+          <t>Aceito. (Nível de Perigo: 20)</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
           <t>Maybe another time.</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L24" s="16" t="inlineStr">
         <is>
           <t>Talvez outra hora.</t>
         </is>
@@ -791,9 +791,9 @@
           <t>Oh, I see... well, if you change your mind, just come talk to me again, okay?</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Ah, entendi... bem, se mudar de ideia, é só vir falar comigo de novo, tá?</t>
+      <c r="L28" s="16" t="inlineStr">
+        <is>
+          <t>Oh, entendo... bom, se mudar de ideia, é só voltar a falar comigo, tá?</t>
         </is>
       </c>
     </row>
@@ -847,10 +847,10 @@
 I just hope Raina and Poina haven’t beaten us to it yet... H-huh? Oh, no, nothing! Nothing at all.</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Sério!? Uau! Muito obrigada. Então vamos nos preparar e partir para a Nefia. A Floresta do Caminho Perdido fica a noroeste daqui.
-Espero que Raina e Poina não tenham chegado antes de nós... H-hã? Ah, não, nada! Nada mesmo.</t>
+      <c r="L34" s="16" t="inlineStr">
+        <is>
+          <t>De verdade!? Ihuu! Muito obrigada. Então vamos nos preparar e partir para a Nefia. A Floresta do Caminho Perdido fica a noroeste daqui.
+Só espero que a Raina e a Poina não tenham chegado lá primeiro... H-hã? Ah, não, nada! Nada nada.</t>
         </is>
       </c>
     </row>
@@ -898,10 +898,10 @@
 Raina and Poina were dead serious this time... there’s no way I could’ve done it alone. Thank you, really, thank you so much.</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Uaaah, conseguimos! Aventureiro, olha—é de verdade! A Bolsa de Armazenamento!
-Raina e Poina estavam falando sério dessa vez... não havia como eu conseguir sozinha. Obrigada, de verdade, muito obrigada.</t>
+      <c r="L41" s="16" t="inlineStr">
+        <is>
+          <t>Waaah, conseguimos! Aventureiro, olha: é real! A Bolsa Guarda-Tudo!
+A Raina e a Poina estavam falando sério desta vez... não tinha como eu fazer isso sozinha. Obrigada, de verdade, muito obrigada.</t>
         </is>
       </c>
     </row>
@@ -934,10 +934,10 @@
 I hope we can go adventuring together again someday. And when we do... let’s stuff this bag full of eggplants and throw a big feast, okay?</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>E aqui está sua recompensa prometida. Sementes raras de árvores que você nunca encontrará nas terras humanas! Até adicionei algumas berinjelas de bônus, direto de mim.
-Espero que possamos sair em aventuras juntas de novo algum dia. E quando isso acontecer... vamos encher essa bolsa de berinjelas e fazer uma grande festa, combinado?</t>
+      <c r="L43" s="16" t="inlineStr">
+        <is>
+          <t>E aqui está a recompensa prometida. Sementes de árvores raras que você nunca acharia nas terras humanas! Ainda coloquei umas berinjelas de bônus, direto de mim.
+Espero que a gente possa aventurar junto de novo um dia. E quando isso acontecer... vamos encher esta bolsa de berinjelas e fazer um banquete, combinado?</t>
         </is>
       </c>
     </row>
@@ -986,9 +986,9 @@
           <t>Huh? That’s weird... my wings feel all tingly... like they’re buzzing with static...</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Hã? Que estranho... minhas asas estão formigando... como se estivessem zumbindo com estática...</t>
+      <c r="L48" s="16" t="inlineStr">
+        <is>
+          <t>Hã? Que esquisito... minhas asas estão formigando... como se estivessem zumbindo de eletricidade...</t>
         </is>
       </c>
     </row>
@@ -1013,10 +1013,10 @@
 Looking for the ‘mystery bag,’ right? Heehee, too bad! See? See this? I already got it!</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Bem, bem. Demorou bastante, Nanasu! Você é tão, tão lenta!
-Procurando pela 'bolsa misteriosa', né? Heehee, azar o seu! Viu? Viu isso? Eu já peguei!</t>
+      <c r="L49" s="16" t="inlineStr">
+        <is>
+          <t>Pois é. Demorou, hein, Nanasu! Você é tããão lenta!
+Procurando a 'bolsa misteriosa', né? Hihi, azar o seu! Viu? Viu isto? Já peguei!</t>
         </is>
       </c>
     </row>
@@ -1039,9 +1039,9 @@
           <t>Raina!? What are you doing here!? That’s the bag I’ve been looking for—give it back!</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Raina!? O que você está fazendo aqui!? Essa é a bolsa que eu estava procurando—devolva!</t>
+      <c r="L50" s="16" t="inlineStr">
+        <is>
+          <t>Raina!? O que você está fazendo aqui!? Essa é a bolsa que eu estava procurando: devolve!</t>
         </is>
       </c>
     </row>
@@ -1064,9 +1064,9 @@
           <t>Give it back? No, no, no, and NO! Treasures in a Nefia go to whoever gets them first. If you want it so badly, why don’t you try taking it from me? Isn’t that why you brought those strong-looking friends of yours?</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Devolver? Não, não, não e NÃO! Tesouros em uma Nefia vão para quem chegar primeiro. Se você quer tanto assim, por que não tenta tirar de mim? Não foi para isso que trouxe esses amigos fortes?</t>
+      <c r="L51" s="16" t="inlineStr">
+        <is>
+          <t>Devolver? Não, não, não e NÃO! Tesouros numa Nefia são de quem pegar primeiro. Se quer tanto assim, por que não tenta tirar de mim? Não é por isso que trouxe esses amigos seus de cara forte?</t>
         </is>
       </c>
     </row>
@@ -1089,9 +1089,9 @@
           <t>Oh, hey there, nice to meetcha, adventurer? I’m Raina, the fairy of thunder! Careful—you might end up all shocky and twitching if you touch me!</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Ah, olá, prazer em conhecê-lo, aventureiro? Eu sou a Raina, a fada do trovão! Cuidado—você pode acabar todo eletrizado e tremendo se me tocar!</t>
+      <c r="L52" s="16" t="inlineStr">
+        <is>
+          <t>Ah, oi, prazer, aventureiro? Sou a Raina, a fada do trovão! Cuidado: você pode acabar todo chocoso e tremelique se me tocar!</t>
         </is>
       </c>
     </row>
@@ -1114,9 +1114,9 @@
           <t>...Noisy. Thanks to your mouth, Raina, we’ve lost the chance to ambush them.</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>...Barulhenta. Graças à sua boca, Raina, perdemos a chance de emboscar eles.</t>
+      <c r="L53" s="16" t="inlineStr">
+        <is>
+          <t>...Barulhenta. Graças a essa sua boca, Raina, perdemos a chance de emboscar eles.</t>
         </is>
       </c>
     </row>
@@ -1139,9 +1139,9 @@
           <t>Aww, come on, Poina! Killing them right away would be boring! Where’s the fun in that?</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Ah, qual é, Poina! Matar eles logo seria chato! Onde está a graça nisso?</t>
+      <c r="L54" s="16" t="inlineStr">
+        <is>
+          <t>Ah, que isso, Poina! Matar logo eles seria chato! Onde está a graça nisso?</t>
         </is>
       </c>
     </row>
@@ -1164,9 +1164,9 @@
           <t>Right, Nanasu? Honestly, I don’t even care about this bag. What I really wanted... was to see that pitiful face of yours. Watching crybaby Nanasu beg ‘stooop it~’ is the best! So ...give it back? NEVER! If you want it, come and fight me for it! Come on, come on, let’s see what you’ve got—I’ll turn you into a roasted eggplant, all nice and crispy with my lightning!</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Certo, Nanasu? Sinceramente, eu nem ligo para essa bolsa. O que eu realmente queria... era ver essa sua cara de coitadinha. Ver a Nanasu chorona implorando 'paaara com isso~' é o máximo! Então... devolver? NUNCA! Se quiser, venha lutar por ela! Vamos, vamos, mostre do que é capaz—vou te transformar em uma berinjela assada, bem crocante com meu raio!</t>
+      <c r="L55" s="16" t="inlineStr">
+        <is>
+          <t>Né, Nanasu? Sinceramente, nem ligo para essa bolsa. O que eu queria de verdade... era ver essa sua cara de coitada. Ver a chorona da Nanasu implorar 'chega~' é o melhor! Então...devolver? JAMAIS! Se quer, vem lutar comigo! Vamos, vamos, mostra do que é capaz: vou te transformar numa berinjela assada, bem crocante com meu relâmpago!</t>
         </is>
       </c>
     </row>
@@ -1189,9 +1189,9 @@
           <t>Idiot... Play around all you want, Raina. But if you get in my way, I’ll kill you too.</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Idiota... Brinque o quanto quiser, Raina. Mas se ficar no meu caminho, vou te matar também.</t>
+      <c r="L56" s="16" t="inlineStr">
+        <is>
+          <t>Idiota... Brinca o quanto quiser, Raina. Mas se atrapalhar meu caminho, mato você também.</t>
         </is>
       </c>
     </row>
@@ -1216,9 +1216,9 @@
           <t>Whoa! Poina is scary as always! But hey, this is getting fun! So then... what do you say, adventurer? Wanna play with us?</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Uau! Poina continua assustadora como sempre! Mas ei, isso está ficando divertido! Então... o que me diz, aventureiro? Quer brincar com a gente?</t>
+      <c r="L57" s="16" t="inlineStr">
+        <is>
+          <t>Eita! A Poina está assustadora como sempre! Mas hey, isso está ficando divertido! Então... que me diz, aventureiro? Quer brincar com a gente?</t>
         </is>
       </c>
     </row>
